--- a/health_tracking_forms/045_daily_health_symptom_log--health_tracking_forms.xlsx
+++ b/health_tracking_forms/045_daily_health_symptom_log--health_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -995,8 +995,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fever'}</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Fever'}</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cough'}</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cough'}</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fatigue'}</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'sore_throat'}</t>
+          <t>sore_throat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Sore throat'}</t>
+          <t>Sore throat</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'headache'}</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Headache'}</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'nausea'}</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Nausea'}</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'diarrhea'}</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Diarrhea'}</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fever'}</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Fever'}</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cough'}</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cough'}</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fatigue'}</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'sore_throat'}</t>
+          <t>sore_throat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Sore throat'}</t>
+          <t>Sore throat</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'headache'}</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Headache'}</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'nausea'}</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Nausea'}</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'diarrhea'}</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Diarrhea'}</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
